--- a/agent_changelog.xlsx
+++ b/agent_changelog.xlsx
@@ -372,7 +372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="4">
@@ -2310,6 +2310,90 @@
       <c r="E63" s="6" t="inlineStr">
         <is>
           <t>v6.66→v6.67 bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>v6.70</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>로컬 검증 게이트 신설 — 게임 위젯 PATCH 위임 전 game/qa 로컬 PASS 확인 의무</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-05-25 Post7 FSM 통합 라이브 사고 — 로컬 검증 없이 PATCH → 버그 라이브 배포</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>로컬 검증 게이트 룰 신설 (F2)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>F2 룰화 작업</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>lead, game, dev, qa, CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>라이브 PATCH 전 로컬 HTML 검증 필수 섹션 신설 (★ 2026-05-25)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-05-25 Post7 FSM 통합 라이브 사고 — CLAUDE.md 프로젝트 룰 반영</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>CLAUDE.md 룰 신설 (F2)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>F2 룰화 작업</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>dev</t>
         </is>
       </c>
     </row>
@@ -2408,27 +2492,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>v1.8</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>v1.9</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>git 운영 룰 + BREAKS Footer 도입</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>라운드테이블 2026-05-25 채택 — git 운영 룰 5개 에이전트 일괄 반영</t>
         </is>
@@ -2539,27 +2623,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>v1.5</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>v1.6</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>git 운영 룰 + BH_queueSound 단일 진입점</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>라운드테이블 2026-05-25 채택 — git 운영 룰 5개 에이전트 일괄 반영</t>
         </is>
@@ -2670,27 +2754,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>v1.7</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>v1.8</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>git 운영 룰 + 2단계 위젯 구조 정책</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>라운드테이블 2026-05-25 채택 — git 운영 룰 5개 에이전트 일괄 반영</t>
         </is>
@@ -4353,27 +4437,27 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>v6.38</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>v6.39</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>git 운영 룰 + LFS 모니터링 책임</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>라운드테이블 2026-05-25 채택 — git 운영 룰 5개 에이전트 일괄 반영</t>
         </is>
@@ -4392,7 +4476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="4">
@@ -5536,6 +5620,28 @@
       <c r="D45" s="6" t="inlineStr">
         <is>
           <t>2026-05-23 Page#303 featured_media:276 카드 이미지 노출 원인 규명 룰화</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>v6.56</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>라이브 PATCH 전 로컬 검증 PASS 확인 필수 룰 신설 — PASS 미첨부 시 PATCH 거부 의무</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-05-25 Post7 FSM 통합 라이브 사고 재발 방지</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="4">
@@ -7030,29 +7136,51 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>v3.43</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>v3.44</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>git 운영 룰 + 인터페이스 약속 추가</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>라운드테이블 2026-05-25 채택 — git 운영 룰 5개 에이전트 일괄 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>v3.45</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>로컬 HTML 검증 절차 신설 — 코드 수정 후 로컬 wrapper.html 플레이 PASS 없이 납품 금지</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-05-25 Post7 FSM 통합 라이브 사고 재발 방지</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="4">
@@ -8207,6 +8335,28 @@
       <c r="D44" s="6" t="inlineStr">
         <is>
           <t>2026-05-23 content.raw 검색만으로 이미지 없음 오진 방지 룰화</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>v8.58</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>로컬 게임 플레이 검수 항목 신설 — 라이브 전용 검수 FAIL 처리, 로컬 체크리스트 의무화</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-05-25 Post7 FSM 통합 라이브 사고 재발 방지</t>
         </is>
       </c>
     </row>

--- a/agent_changelog.xlsx
+++ b/agent_changelog.xlsx
@@ -2314,84 +2314,84 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>v6.70</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>로컬 검증 게이트 신설 — 게임 위젯 PATCH 위임 전 game/qa 로컬 PASS 확인 의무</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>2026-05-25 Post7 FSM 통합 라이브 사고 — 로컬 검증 없이 PATCH → 버그 라이브 배포</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="6" t="inlineStr">
         <is>
           <t>로컬 검증 게이트 룰 신설 (F2)</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <t>F2 룰화 작업</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="6" t="inlineStr">
         <is>
           <t>lead, game, dev, qa, CLAUDE.md</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>dev</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>CLAUDE.md</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>라이브 PATCH 전 로컬 HTML 검증 필수 섹션 신설 (★ 2026-05-25)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>2026-05-25 Post7 FSM 통합 라이브 사고 — CLAUDE.md 프로젝트 룰 반영</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>CLAUDE.md 룰 신설 (F2)</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <t>F2 룰화 작업</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="6" t="inlineStr">
         <is>
           <t>CLAUDE.md</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>dev</t>
         </is>
@@ -5624,22 +5624,22 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>v6.56</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>라이브 PATCH 전 로컬 검증 PASS 확인 필수 룰 신설 — PASS 미첨부 시 PATCH 거부 의무</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>2026-05-25 Post7 FSM 통합 라이브 사고 재발 방지</t>
         </is>
@@ -6212,7 +6212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="4">
@@ -7163,24 +7163,46 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>v3.45</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>로컬 HTML 검증 절차 신설 — 코드 수정 후 로컬 wrapper.html 플레이 PASS 없이 납품 금지</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>2026-05-25 Post7 FSM 통합 라이브 사고 재발 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>v3.45 -&gt; v3.46</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>정본 코드 동기화 11건 현행화</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>카드 데이터 모델(yeol-&gt;jo, ddi-&gt;dan, ribbon/special 폐기, emoji/svgUrl 추가) + BH_GS 4상태 phase + playerCaptured/aiCaptured + priority 배열 + AI Hard 휴리스틱+jokbo + FSM 사고 박스 + 족보 판정/카드 정의/localStorage 보류 박스 5개 + 카드 크기 60x84px 완화 + CSS 3D flip 보류. 분류기 Self-Modification 차단으로 사용자 직접 편집. 보호 박스 추가로 F4 잔존 모두 의도된 참조용 보존 영역 포함. 정본 위젯 F2(min-height:420px) 함께 진행. SHA: BE72CA1A...</t>
         </is>
       </c>
     </row>
@@ -8339,22 +8361,22 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>v8.58</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>로컬 게임 플레이 검수 항목 신설 — 라이브 전용 검수 FAIL 처리, 로컬 체크리스트 의무화</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>2026-05-25 Post7 FSM 통합 라이브 사고 재발 방지</t>
         </is>
